--- a/X-Series/XD12R/Jig/XCR_XDR/XC24RV_XD12RV/Docs/GT/XD_register_초기 구동_260708_jylee_답변.xlsx
+++ b/X-Series/XD12R/Jig/XCR_XDR/XC24RV_XD12RV/Docs/GT/XD_register_초기 구동_260708_jylee_답변.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD12R\Jig\XCR_XDR\XC24RV_XD12RV\Docs\GT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBEB8978-03FB-4DDB-B5BC-E02DE4B8F736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ED3F5F-2368-4870-A2C8-57C3C41DCB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="812" xr2:uid="{6E253F25-89D9-4CFB-91D3-179DBBF2E33D}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="812" xr2:uid="{6E253F25-89D9-4CFB-91D3-179DBBF2E33D}"/>
   </bookViews>
   <sheets>
     <sheet name="xd12r_reg_mp1" sheetId="170" r:id="rId1"/>
@@ -1981,10 +1981,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0x417</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1/2 분주 clock 이 사용 됨으로,
 기존 대비 1/2 수준으로 수정</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2008,6 +2004,10 @@
   </si>
   <si>
     <t>SYNC_MODE =1 에 따른 register 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x41E</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2477,128 +2477,128 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3108,7 +3108,7 @@
       <c r="U2" s="57" t="s">
         <v>369</v>
       </c>
-      <c r="V2" s="101" t="s">
+      <c r="V2" s="63" t="s">
         <v>373</v>
       </c>
       <c r="W2" s="18" t="s">
@@ -3146,13 +3146,13 @@
       <c r="L3" s="11"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="90" t="s">
+      <c r="O3" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="90"/>
-      <c r="S3" s="89"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="67"/>
       <c r="T3" s="50" t="s">
         <v>225</v>
       </c>
@@ -3180,14 +3180,14 @@
         <v>19</v>
       </c>
       <c r="H4" s="11"/>
-      <c r="I4" s="69" t="s">
+      <c r="I4" s="71" t="s">
         <v>309</v>
       </c>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="84"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="73"/>
       <c r="O4" s="14" t="s">
         <v>310</v>
       </c>
@@ -3203,8 +3203,8 @@
       <c r="S4" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="T4" s="102" t="s">
-        <v>375</v>
+      <c r="T4" s="64" t="s">
+        <v>381</v>
       </c>
       <c r="U4" s="58" t="s">
         <v>370</v>
@@ -3240,13 +3240,13 @@
       <c r="L5" s="25"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
-      <c r="O5" s="73" t="s">
+      <c r="O5" s="68" t="s">
         <v>226</v>
       </c>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="77"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="69"/>
       <c r="T5" s="51" t="s">
         <v>355</v>
       </c>
@@ -3273,22 +3273,22 @@
       <c r="F6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="70" t="s">
         <v>140</v>
       </c>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68" t="s">
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70" t="s">
         <v>139</v>
       </c>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="69"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="71"/>
       <c r="T6" s="50" t="s">
         <v>356</v>
       </c>
@@ -3315,22 +3315,22 @@
       <c r="F7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="68" t="s">
+      <c r="H7" s="70" t="s">
         <v>142</v>
       </c>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="68"/>
-      <c r="P7" s="68" t="s">
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="Q7" s="68"/>
-      <c r="R7" s="68"/>
-      <c r="S7" s="69"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="71"/>
       <c r="T7" s="50" t="s">
         <v>357</v>
       </c>
@@ -3417,16 +3417,16 @@
       <c r="F9" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="99" t="s">
+      <c r="H9" s="76" t="s">
         <v>313</v>
       </c>
-      <c r="I9" s="84"/>
-      <c r="J9" s="75" t="s">
+      <c r="I9" s="73"/>
+      <c r="J9" s="77" t="s">
         <v>314</v>
       </c>
-      <c r="K9" s="100"/>
-      <c r="L9" s="100"/>
-      <c r="M9" s="76"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="78"/>
+      <c r="M9" s="79"/>
       <c r="N9" s="11" t="s">
         <v>222</v>
       </c>
@@ -3471,30 +3471,30 @@
       <c r="F10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="86" t="s">
+      <c r="H10" s="80" t="s">
         <v>295</v>
       </c>
-      <c r="I10" s="87"/>
-      <c r="J10" s="86" t="s">
+      <c r="I10" s="81"/>
+      <c r="J10" s="80" t="s">
         <v>296</v>
       </c>
-      <c r="K10" s="87"/>
-      <c r="L10" s="86" t="s">
+      <c r="K10" s="81"/>
+      <c r="L10" s="80" t="s">
         <v>297</v>
       </c>
-      <c r="M10" s="87"/>
-      <c r="N10" s="86" t="s">
+      <c r="M10" s="81"/>
+      <c r="N10" s="80" t="s">
         <v>298</v>
       </c>
-      <c r="O10" s="87"/>
-      <c r="P10" s="86" t="s">
+      <c r="O10" s="81"/>
+      <c r="P10" s="80" t="s">
         <v>299</v>
       </c>
-      <c r="Q10" s="87"/>
-      <c r="R10" s="86" t="s">
+      <c r="Q10" s="81"/>
+      <c r="R10" s="80" t="s">
         <v>318</v>
       </c>
-      <c r="S10" s="88"/>
+      <c r="S10" s="82"/>
       <c r="T10" s="50" t="s">
         <v>359</v>
       </c>
@@ -3521,30 +3521,30 @@
       <c r="F11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="86" t="s">
+      <c r="H11" s="80" t="s">
         <v>300</v>
       </c>
-      <c r="I11" s="87"/>
-      <c r="J11" s="86" t="s">
+      <c r="I11" s="81"/>
+      <c r="J11" s="80" t="s">
         <v>301</v>
       </c>
-      <c r="K11" s="87"/>
-      <c r="L11" s="86" t="s">
+      <c r="K11" s="81"/>
+      <c r="L11" s="80" t="s">
         <v>302</v>
       </c>
-      <c r="M11" s="87"/>
-      <c r="N11" s="86" t="s">
+      <c r="M11" s="81"/>
+      <c r="N11" s="80" t="s">
         <v>303</v>
       </c>
-      <c r="O11" s="87"/>
-      <c r="P11" s="86" t="s">
+      <c r="O11" s="81"/>
+      <c r="P11" s="80" t="s">
         <v>304</v>
       </c>
-      <c r="Q11" s="87"/>
-      <c r="R11" s="86" t="s">
+      <c r="Q11" s="81"/>
+      <c r="R11" s="80" t="s">
         <v>305</v>
       </c>
-      <c r="S11" s="88"/>
+      <c r="S11" s="82"/>
       <c r="T11" s="50" t="s">
         <v>359</v>
       </c>
@@ -3629,20 +3629,20 @@
       <c r="F13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="89" t="s">
+      <c r="H13" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="83"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="83"/>
-      <c r="Q13" s="83"/>
-      <c r="R13" s="83"/>
-      <c r="S13" s="83"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
       <c r="T13" s="52" t="s">
         <v>364</v>
       </c>
@@ -3669,20 +3669,20 @@
       <c r="F14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="89" t="s">
+      <c r="H14" s="67" t="s">
         <v>264</v>
       </c>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="83"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="83"/>
-      <c r="R14" s="83"/>
-      <c r="S14" s="83"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
       <c r="T14" s="52" t="s">
         <v>365</v>
       </c>
@@ -3709,20 +3709,20 @@
       <c r="F15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="90" t="s">
+      <c r="H15" s="66" t="s">
         <v>265</v>
       </c>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="90"/>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="90"/>
-      <c r="S15" s="89"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="67"/>
       <c r="T15" s="52" t="s">
         <v>365</v>
       </c>
@@ -3749,20 +3749,20 @@
       <c r="F16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="91" t="s">
+      <c r="H16" s="83" t="s">
         <v>322</v>
       </c>
-      <c r="I16" s="91"/>
-      <c r="J16" s="91"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="91"/>
-      <c r="M16" s="91"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="91"/>
-      <c r="P16" s="91"/>
-      <c r="Q16" s="91"/>
-      <c r="R16" s="91"/>
-      <c r="S16" s="86"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="83"/>
+      <c r="N16" s="83"/>
+      <c r="O16" s="83"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="83"/>
+      <c r="R16" s="83"/>
+      <c r="S16" s="80"/>
       <c r="T16" s="50" t="s">
         <v>19</v>
       </c>
@@ -3789,20 +3789,20 @@
       <c r="F17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="91" t="s">
+      <c r="H17" s="83" t="s">
         <v>324</v>
       </c>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="86"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="83"/>
+      <c r="K17" s="83"/>
+      <c r="L17" s="83"/>
+      <c r="M17" s="83"/>
+      <c r="N17" s="83"/>
+      <c r="O17" s="83"/>
+      <c r="P17" s="83"/>
+      <c r="Q17" s="83"/>
+      <c r="R17" s="83"/>
+      <c r="S17" s="80"/>
       <c r="T17" s="50" t="s">
         <v>19</v>
       </c>
@@ -3820,18 +3820,18 @@
       <c r="E18" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H18" s="82"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="82"/>
-      <c r="R18" s="83"/>
-      <c r="S18" s="83"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
       <c r="T18" s="50"/>
       <c r="U18" s="11"/>
       <c r="V18" s="11"/>
@@ -3856,20 +3856,20 @@
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
-      <c r="J19" s="68" t="s">
+      <c r="J19" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="K19" s="68"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="68" t="s">
+      <c r="K19" s="70"/>
+      <c r="L19" s="70"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="69"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="70"/>
+      <c r="R19" s="70"/>
+      <c r="S19" s="71"/>
       <c r="T19" s="50" t="s">
         <v>19</v>
       </c>
@@ -3898,20 +3898,20 @@
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
-      <c r="J20" s="68" t="s">
+      <c r="J20" s="70" t="s">
         <v>148</v>
       </c>
-      <c r="K20" s="68"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="68" t="s">
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="70" t="s">
         <v>147</v>
       </c>
-      <c r="P20" s="68"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="69"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="71"/>
       <c r="T20" s="50" t="s">
         <v>19</v>
       </c>
@@ -3938,20 +3938,20 @@
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
-      <c r="J21" s="68" t="s">
+      <c r="J21" s="70" t="s">
         <v>150</v>
       </c>
-      <c r="K21" s="68"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="68" t="s">
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="70" t="s">
         <v>149</v>
       </c>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="69"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="70"/>
+      <c r="S21" s="71"/>
       <c r="T21" s="50" t="s">
         <v>19</v>
       </c>
@@ -3978,20 +3978,20 @@
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
-      <c r="J22" s="68" t="s">
+      <c r="J22" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="K22" s="68"/>
-      <c r="L22" s="68"/>
-      <c r="M22" s="68"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="68" t="s">
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="P22" s="68"/>
-      <c r="Q22" s="68"/>
-      <c r="R22" s="68"/>
-      <c r="S22" s="69"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="71"/>
       <c r="T22" s="50" t="s">
         <v>19</v>
       </c>
@@ -4018,20 +4018,20 @@
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
-      <c r="J23" s="68" t="s">
+      <c r="J23" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="K23" s="68"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="68" t="s">
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="68"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="69"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
+      <c r="S23" s="71"/>
       <c r="T23" s="50" t="s">
         <v>19</v>
       </c>
@@ -4058,20 +4058,20 @@
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
-      <c r="J24" s="68" t="s">
+      <c r="J24" s="70" t="s">
         <v>156</v>
       </c>
-      <c r="K24" s="68"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="68" t="s">
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="P24" s="68"/>
-      <c r="Q24" s="68"/>
-      <c r="R24" s="68"/>
-      <c r="S24" s="69"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="70"/>
+      <c r="R24" s="70"/>
+      <c r="S24" s="71"/>
       <c r="T24" s="50" t="s">
         <v>19</v>
       </c>
@@ -4096,26 +4096,26 @@
       <c r="F25" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="80" t="s">
+      <c r="H25" s="85" t="s">
         <v>326</v>
       </c>
-      <c r="I25" s="80"/>
-      <c r="J25" s="80"/>
-      <c r="K25" s="79" t="s">
+      <c r="I25" s="85"/>
+      <c r="J25" s="85"/>
+      <c r="K25" s="86" t="s">
         <v>169</v>
       </c>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="79" t="s">
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="O25" s="79"/>
-      <c r="P25" s="79"/>
-      <c r="Q25" s="79" t="s">
+      <c r="O25" s="86"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="R25" s="79"/>
-      <c r="S25" s="96"/>
+      <c r="R25" s="86"/>
+      <c r="S25" s="87"/>
       <c r="T25" s="53" t="s">
         <v>367</v>
       </c>
@@ -4140,26 +4140,26 @@
       <c r="F26" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="79" t="s">
+      <c r="H26" s="86" t="s">
         <v>214</v>
       </c>
-      <c r="I26" s="79"/>
-      <c r="J26" s="79"/>
-      <c r="K26" s="96" t="s">
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="87" t="s">
         <v>213</v>
       </c>
-      <c r="L26" s="97"/>
-      <c r="M26" s="98"/>
-      <c r="N26" s="79" t="s">
+      <c r="L26" s="93"/>
+      <c r="M26" s="94"/>
+      <c r="N26" s="86" t="s">
         <v>212</v>
       </c>
-      <c r="O26" s="79"/>
-      <c r="P26" s="79"/>
-      <c r="Q26" s="80" t="s">
+      <c r="O26" s="86"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="85" t="s">
         <v>329</v>
       </c>
-      <c r="R26" s="80"/>
-      <c r="S26" s="81"/>
+      <c r="R26" s="85"/>
+      <c r="S26" s="95"/>
       <c r="T26" s="53" t="s">
         <v>367</v>
       </c>
@@ -4190,16 +4190,16 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
-      <c r="N27" s="80" t="s">
+      <c r="N27" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="O27" s="80"/>
-      <c r="P27" s="80"/>
-      <c r="Q27" s="80" t="s">
+      <c r="O27" s="85"/>
+      <c r="P27" s="85"/>
+      <c r="Q27" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="R27" s="80"/>
-      <c r="S27" s="81"/>
+      <c r="R27" s="85"/>
+      <c r="S27" s="95"/>
       <c r="T27" s="54"/>
       <c r="U27" s="61"/>
       <c r="V27" s="61"/>
@@ -4222,24 +4222,24 @@
       <c r="F28" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H28" s="92" t="s">
+      <c r="H28" s="89" t="s">
         <v>260</v>
       </c>
-      <c r="I28" s="92"/>
-      <c r="J28" s="92"/>
-      <c r="K28" s="92"/>
-      <c r="L28" s="92" t="s">
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
+      <c r="L28" s="89" t="s">
         <v>261</v>
       </c>
-      <c r="M28" s="92"/>
-      <c r="N28" s="92"/>
-      <c r="O28" s="92"/>
-      <c r="P28" s="92" t="s">
+      <c r="M28" s="89"/>
+      <c r="N28" s="89"/>
+      <c r="O28" s="89"/>
+      <c r="P28" s="89" t="s">
         <v>262</v>
       </c>
-      <c r="Q28" s="92"/>
-      <c r="R28" s="92"/>
-      <c r="S28" s="93"/>
+      <c r="Q28" s="89"/>
+      <c r="R28" s="89"/>
+      <c r="S28" s="90"/>
       <c r="T28" s="54" t="s">
         <v>366</v>
       </c>
@@ -4270,18 +4270,18 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
-      <c r="L29" s="94" t="s">
+      <c r="L29" s="91" t="s">
         <v>336</v>
       </c>
-      <c r="M29" s="94"/>
-      <c r="N29" s="94"/>
-      <c r="O29" s="94"/>
-      <c r="P29" s="94" t="s">
+      <c r="M29" s="91"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="91"/>
+      <c r="P29" s="91" t="s">
         <v>337</v>
       </c>
-      <c r="Q29" s="94"/>
-      <c r="R29" s="94"/>
-      <c r="S29" s="95"/>
+      <c r="Q29" s="91"/>
+      <c r="R29" s="91"/>
+      <c r="S29" s="92"/>
       <c r="T29" s="54" t="s">
         <v>19</v>
       </c>
@@ -4311,9 +4311,9 @@
       <c r="K30" s="42"/>
       <c r="L30" s="34"/>
       <c r="M30" s="38"/>
-      <c r="N30" s="82"/>
-      <c r="O30" s="83"/>
-      <c r="P30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="73"/>
       <c r="Q30" s="42"/>
       <c r="R30" s="34"/>
       <c r="S30" s="48" t="s">
@@ -4345,30 +4345,30 @@
       <c r="F31" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="H31" s="68" t="s">
+      <c r="H31" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
-      <c r="L31" s="68"/>
-      <c r="M31" s="68"/>
-      <c r="N31" s="68" t="s">
+      <c r="I31" s="70"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="70" t="s">
         <v>122</v>
       </c>
-      <c r="O31" s="68"/>
-      <c r="P31" s="68"/>
-      <c r="Q31" s="68"/>
-      <c r="R31" s="68"/>
-      <c r="S31" s="69"/>
-      <c r="T31" s="103" t="s">
-        <v>377</v>
+      <c r="O31" s="70"/>
+      <c r="P31" s="70"/>
+      <c r="Q31" s="70"/>
+      <c r="R31" s="70"/>
+      <c r="S31" s="71"/>
+      <c r="T31" s="65" t="s">
+        <v>376</v>
       </c>
       <c r="U31" s="58" t="s">
         <v>371</v>
       </c>
       <c r="V31" s="58" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="W31" s="19" t="s">
         <v>251</v>
@@ -4394,17 +4394,17 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
-      <c r="K32" s="68" t="s">
+      <c r="K32" s="70" t="s">
         <v>181</v>
       </c>
-      <c r="L32" s="68"/>
-      <c r="M32" s="68"/>
-      <c r="N32" s="68"/>
-      <c r="O32" s="68"/>
-      <c r="P32" s="68"/>
-      <c r="Q32" s="68"/>
-      <c r="R32" s="68"/>
-      <c r="S32" s="69"/>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="70"/>
+      <c r="R32" s="70"/>
+      <c r="S32" s="71"/>
       <c r="T32" s="50" t="s">
         <v>182</v>
       </c>
@@ -4433,24 +4433,24 @@
       </c>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
-      <c r="J33" s="68" t="s">
+      <c r="J33" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="K33" s="68"/>
-      <c r="L33" s="68"/>
-      <c r="M33" s="68"/>
-      <c r="N33" s="68"/>
-      <c r="O33" s="68"/>
-      <c r="P33" s="68"/>
-      <c r="Q33" s="68"/>
-      <c r="R33" s="68"/>
-      <c r="S33" s="69"/>
-      <c r="T33" s="103" t="s">
-        <v>379</v>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="70"/>
+      <c r="R33" s="70"/>
+      <c r="S33" s="71"/>
+      <c r="T33" s="65" t="s">
+        <v>378</v>
       </c>
       <c r="U33" s="11"/>
       <c r="V33" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="W33" s="19" t="s">
         <v>257</v>
@@ -4477,24 +4477,24 @@
         <v>195</v>
       </c>
       <c r="I34" s="11"/>
-      <c r="J34" s="68" t="s">
+      <c r="J34" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="K34" s="68"/>
-      <c r="L34" s="68"/>
-      <c r="M34" s="68"/>
-      <c r="N34" s="68"/>
-      <c r="O34" s="68"/>
-      <c r="P34" s="68"/>
-      <c r="Q34" s="68"/>
-      <c r="R34" s="68"/>
-      <c r="S34" s="69"/>
-      <c r="T34" s="103" t="s">
-        <v>380</v>
+      <c r="K34" s="70"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="70"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="70"/>
+      <c r="Q34" s="70"/>
+      <c r="R34" s="70"/>
+      <c r="S34" s="71"/>
+      <c r="T34" s="65" t="s">
+        <v>379</v>
       </c>
       <c r="U34" s="11"/>
       <c r="V34" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="W34" s="19" t="s">
         <v>257</v>
@@ -4519,18 +4519,18 @@
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="68" t="s">
+      <c r="J35" s="70" t="s">
         <v>184</v>
       </c>
-      <c r="K35" s="68"/>
-      <c r="L35" s="68"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="68"/>
-      <c r="O35" s="68"/>
-      <c r="P35" s="68"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="68"/>
-      <c r="S35" s="69"/>
+      <c r="K35" s="70"/>
+      <c r="L35" s="70"/>
+      <c r="M35" s="70"/>
+      <c r="N35" s="70"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="70"/>
+      <c r="Q35" s="70"/>
+      <c r="R35" s="70"/>
+      <c r="S35" s="71"/>
       <c r="T35" s="50" t="s">
         <v>19</v>
       </c>
@@ -4558,19 +4558,19 @@
         <v>360</v>
       </c>
       <c r="H36" s="12"/>
-      <c r="I36" s="68" t="s">
+      <c r="I36" s="70" t="s">
         <v>252</v>
       </c>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="68"/>
-      <c r="M36" s="68"/>
-      <c r="N36" s="68"/>
-      <c r="O36" s="68"/>
-      <c r="P36" s="68"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="69"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="70"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
+      <c r="S36" s="71"/>
       <c r="T36" s="50" t="s">
         <v>107</v>
       </c>
@@ -4597,20 +4597,20 @@
       <c r="F37" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H37" s="68" t="s">
+      <c r="H37" s="70" t="s">
         <v>229</v>
       </c>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
-      <c r="L37" s="68"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="68"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="68"/>
-      <c r="Q37" s="68"/>
-      <c r="R37" s="68"/>
-      <c r="S37" s="69"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="70"/>
+      <c r="N37" s="70"/>
+      <c r="O37" s="70"/>
+      <c r="P37" s="70"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="70"/>
+      <c r="S37" s="71"/>
       <c r="T37" s="50" t="s">
         <v>362</v>
       </c>
@@ -4640,21 +4640,21 @@
       <c r="H38" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="I38" s="68" t="s">
+      <c r="I38" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="J38" s="68"/>
+      <c r="J38" s="70"/>
       <c r="K38" s="11"/>
-      <c r="L38" s="68" t="s">
+      <c r="L38" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="M38" s="68"/>
-      <c r="N38" s="68"/>
-      <c r="O38" s="68"/>
-      <c r="P38" s="68"/>
-      <c r="Q38" s="68"/>
-      <c r="R38" s="68"/>
-      <c r="S38" s="69"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
+      <c r="S38" s="71"/>
       <c r="T38" s="50" t="s">
         <v>361</v>
       </c>
@@ -4692,20 +4692,20 @@
       <c r="F40" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="H40" s="85" t="s">
+      <c r="H40" s="88" t="s">
         <v>218</v>
       </c>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="68"/>
-      <c r="S40" s="69"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="70"/>
+      <c r="N40" s="70"/>
+      <c r="O40" s="70"/>
+      <c r="P40" s="70"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="70"/>
+      <c r="S40" s="71"/>
       <c r="T40" s="50" t="s">
         <v>219</v>
       </c>
@@ -4732,14 +4732,14 @@
       <c r="F41" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H41" s="68" t="s">
+      <c r="H41" s="70" t="s">
         <v>187</v>
       </c>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="68"/>
-      <c r="M41" s="68"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
       <c r="N41" s="14" t="s">
         <v>306</v>
       </c>
@@ -4832,30 +4832,30 @@
       <c r="F43" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="H43" s="68" t="s">
+      <c r="H43" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
       <c r="L43" s="14" t="s">
         <v>345</v>
       </c>
       <c r="M43" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="N43" s="68" t="s">
+      <c r="N43" s="70" t="s">
         <v>128</v>
       </c>
-      <c r="O43" s="68"/>
-      <c r="P43" s="78" t="s">
+      <c r="O43" s="70"/>
+      <c r="P43" s="96" t="s">
         <v>179</v>
       </c>
-      <c r="Q43" s="78"/>
-      <c r="R43" s="68" t="s">
+      <c r="Q43" s="96"/>
+      <c r="R43" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="S43" s="69"/>
+      <c r="S43" s="71"/>
       <c r="T43" s="50" t="s">
         <v>344</v>
       </c>
@@ -4880,20 +4880,20 @@
       <c r="F44" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H44" s="68" t="s">
+      <c r="H44" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="I44" s="68"/>
-      <c r="J44" s="68"/>
-      <c r="K44" s="68"/>
-      <c r="L44" s="68"/>
-      <c r="M44" s="68"/>
-      <c r="N44" s="68"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="68"/>
-      <c r="Q44" s="68"/>
-      <c r="R44" s="68"/>
-      <c r="S44" s="69"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="70"/>
+      <c r="M44" s="70"/>
+      <c r="N44" s="70"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="70"/>
+      <c r="Q44" s="70"/>
+      <c r="R44" s="70"/>
+      <c r="S44" s="71"/>
       <c r="T44" s="50" t="s">
         <v>19</v>
       </c>
@@ -4926,16 +4926,16 @@
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
-      <c r="N45" s="73" t="s">
+      <c r="N45" s="68" t="s">
         <v>239</v>
       </c>
-      <c r="O45" s="73"/>
-      <c r="P45" s="68" t="s">
+      <c r="O45" s="68"/>
+      <c r="P45" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="Q45" s="68"/>
-      <c r="R45" s="68"/>
-      <c r="S45" s="69"/>
+      <c r="Q45" s="70"/>
+      <c r="R45" s="70"/>
+      <c r="S45" s="71"/>
       <c r="T45" s="50" t="s">
         <v>125</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>372</v>
       </c>
       <c r="V45" s="58" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="W45" s="19"/>
     </row>
@@ -4972,17 +4972,17 @@
       <c r="J46" s="25"/>
       <c r="K46" s="25"/>
       <c r="L46" s="25"/>
-      <c r="M46" s="73" t="s">
+      <c r="M46" s="68" t="s">
         <v>242</v>
       </c>
-      <c r="N46" s="73"/>
-      <c r="O46" s="73"/>
+      <c r="N46" s="68"/>
+      <c r="O46" s="68"/>
       <c r="P46" s="25"/>
-      <c r="Q46" s="73" t="s">
+      <c r="Q46" s="68" t="s">
         <v>243</v>
       </c>
-      <c r="R46" s="73"/>
-      <c r="S46" s="77"/>
+      <c r="R46" s="68"/>
+      <c r="S46" s="69"/>
       <c r="T46" s="51" t="s">
         <v>19</v>
       </c>
@@ -5095,16 +5095,16 @@
       <c r="H51" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I51" s="73" t="s">
+      <c r="I51" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="J51" s="73"/>
-      <c r="K51" s="73"/>
-      <c r="L51" s="74" t="s">
+      <c r="J51" s="68"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="101" t="s">
         <v>348</v>
       </c>
-      <c r="M51" s="75"/>
-      <c r="N51" s="76"/>
+      <c r="M51" s="77"/>
+      <c r="N51" s="79"/>
       <c r="O51" s="14" t="s">
         <v>173</v>
       </c>
@@ -5153,12 +5153,12 @@
       <c r="M52" s="11"/>
       <c r="N52" s="11"/>
       <c r="O52" s="11"/>
-      <c r="P52" s="68" t="s">
+      <c r="P52" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="Q52" s="68"/>
-      <c r="R52" s="68"/>
-      <c r="S52" s="69"/>
+      <c r="Q52" s="70"/>
+      <c r="R52" s="70"/>
+      <c r="S52" s="71"/>
       <c r="T52" s="50" t="s">
         <v>19</v>
       </c>
@@ -5185,20 +5185,20 @@
       <c r="F53" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="H53" s="68" t="s">
+      <c r="H53" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="I53" s="68"/>
-      <c r="J53" s="68"/>
-      <c r="K53" s="68"/>
-      <c r="L53" s="68"/>
-      <c r="M53" s="68"/>
-      <c r="N53" s="68"/>
-      <c r="O53" s="68"/>
-      <c r="P53" s="68"/>
-      <c r="Q53" s="68"/>
-      <c r="R53" s="68"/>
-      <c r="S53" s="69"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="70"/>
+      <c r="K53" s="70"/>
+      <c r="L53" s="70"/>
+      <c r="M53" s="70"/>
+      <c r="N53" s="70"/>
+      <c r="O53" s="70"/>
+      <c r="P53" s="70"/>
+      <c r="Q53" s="70"/>
+      <c r="R53" s="70"/>
+      <c r="S53" s="71"/>
       <c r="T53" s="50" t="s">
         <v>107</v>
       </c>
@@ -5231,16 +5231,16 @@
       <c r="K54" s="11"/>
       <c r="L54" s="11"/>
       <c r="M54" s="11"/>
-      <c r="N54" s="68" t="s">
+      <c r="N54" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="O54" s="68"/>
-      <c r="P54" s="68" t="s">
+      <c r="O54" s="70"/>
+      <c r="P54" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="Q54" s="68"/>
-      <c r="R54" s="68"/>
-      <c r="S54" s="69"/>
+      <c r="Q54" s="70"/>
+      <c r="R54" s="70"/>
+      <c r="S54" s="71"/>
       <c r="T54" s="50" t="s">
         <v>71</v>
       </c>
@@ -5311,20 +5311,20 @@
       <c r="F56" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="H56" s="68" t="s">
+      <c r="H56" s="70" t="s">
         <v>175</v>
       </c>
-      <c r="I56" s="68"/>
-      <c r="J56" s="68"/>
-      <c r="K56" s="68"/>
-      <c r="L56" s="68"/>
-      <c r="M56" s="68"/>
-      <c r="N56" s="68"/>
-      <c r="O56" s="68"/>
-      <c r="P56" s="68"/>
-      <c r="Q56" s="68"/>
-      <c r="R56" s="68"/>
-      <c r="S56" s="69"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="70"/>
+      <c r="K56" s="70"/>
+      <c r="L56" s="70"/>
+      <c r="M56" s="70"/>
+      <c r="N56" s="70"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="70"/>
+      <c r="Q56" s="70"/>
+      <c r="R56" s="70"/>
+      <c r="S56" s="71"/>
       <c r="T56" s="50" t="s">
         <v>124</v>
       </c>
@@ -5445,16 +5445,16 @@
       <c r="I61" s="25"/>
       <c r="J61" s="25"/>
       <c r="K61" s="25"/>
-      <c r="L61" s="67" t="s">
+      <c r="L61" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="M61" s="67"/>
-      <c r="N61" s="67"/>
-      <c r="O61" s="67"/>
-      <c r="P61" s="67"/>
-      <c r="Q61" s="67"/>
-      <c r="R61" s="67"/>
-      <c r="S61" s="65"/>
+      <c r="M61" s="97"/>
+      <c r="N61" s="97"/>
+      <c r="O61" s="97"/>
+      <c r="P61" s="97"/>
+      <c r="Q61" s="97"/>
+      <c r="R61" s="97"/>
+      <c r="S61" s="74"/>
       <c r="T61" s="51"/>
       <c r="U61" s="25"/>
       <c r="V61" s="25"/>
@@ -5478,20 +5478,20 @@
       </c>
       <c r="H62" s="35"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="67" t="s">
+      <c r="J62" s="97" t="s">
         <v>208</v>
       </c>
-      <c r="K62" s="70"/>
-      <c r="L62" s="70"/>
-      <c r="M62" s="70"/>
-      <c r="N62" s="70"/>
-      <c r="O62" s="67" t="s">
+      <c r="K62" s="98"/>
+      <c r="L62" s="98"/>
+      <c r="M62" s="98"/>
+      <c r="N62" s="98"/>
+      <c r="O62" s="97" t="s">
         <v>209</v>
       </c>
-      <c r="P62" s="70"/>
-      <c r="Q62" s="70"/>
-      <c r="R62" s="70"/>
-      <c r="S62" s="71"/>
+      <c r="P62" s="98"/>
+      <c r="Q62" s="98"/>
+      <c r="R62" s="98"/>
+      <c r="S62" s="99"/>
       <c r="T62" s="51"/>
       <c r="U62" s="25"/>
       <c r="V62" s="25"/>
@@ -5515,22 +5515,22 @@
         <v>293</v>
       </c>
       <c r="G63" s="10"/>
-      <c r="H63" s="65" t="s">
+      <c r="H63" s="74" t="s">
         <v>291</v>
       </c>
-      <c r="I63" s="66"/>
-      <c r="J63" s="66"/>
-      <c r="K63" s="66"/>
-      <c r="L63" s="72"/>
+      <c r="I63" s="75"/>
+      <c r="J63" s="75"/>
+      <c r="K63" s="75"/>
+      <c r="L63" s="100"/>
       <c r="M63" s="25"/>
       <c r="N63" s="25"/>
-      <c r="O63" s="65" t="s">
+      <c r="O63" s="74" t="s">
         <v>290</v>
       </c>
-      <c r="P63" s="66"/>
-      <c r="Q63" s="66"/>
-      <c r="R63" s="66"/>
-      <c r="S63" s="66"/>
+      <c r="P63" s="75"/>
+      <c r="Q63" s="75"/>
+      <c r="R63" s="75"/>
+      <c r="S63" s="75"/>
       <c r="T63" s="51"/>
       <c r="U63" s="25"/>
       <c r="V63" s="25"/>
@@ -5558,18 +5558,18 @@
       <c r="I64" s="25"/>
       <c r="J64" s="25"/>
       <c r="K64" s="25"/>
-      <c r="L64" s="67" t="s">
+      <c r="L64" s="97" t="s">
         <v>210</v>
       </c>
-      <c r="M64" s="67"/>
-      <c r="N64" s="67"/>
-      <c r="O64" s="67"/>
-      <c r="P64" s="67" t="s">
+      <c r="M64" s="97"/>
+      <c r="N64" s="97"/>
+      <c r="O64" s="97"/>
+      <c r="P64" s="97" t="s">
         <v>211</v>
       </c>
-      <c r="Q64" s="67"/>
-      <c r="R64" s="67"/>
-      <c r="S64" s="65"/>
+      <c r="Q64" s="97"/>
+      <c r="R64" s="97"/>
+      <c r="S64" s="74"/>
       <c r="T64" s="51"/>
       <c r="U64" s="25"/>
       <c r="V64" s="25"/>
@@ -5596,17 +5596,17 @@
       <c r="H65" s="25"/>
       <c r="I65" s="25"/>
       <c r="J65" s="25"/>
-      <c r="K65" s="65" t="s">
+      <c r="K65" s="74" t="s">
         <v>266</v>
       </c>
-      <c r="L65" s="66"/>
-      <c r="M65" s="66"/>
-      <c r="N65" s="66"/>
-      <c r="O65" s="66"/>
-      <c r="P65" s="66"/>
-      <c r="Q65" s="66"/>
-      <c r="R65" s="66"/>
-      <c r="S65" s="66"/>
+      <c r="L65" s="75"/>
+      <c r="M65" s="75"/>
+      <c r="N65" s="75"/>
+      <c r="O65" s="75"/>
+      <c r="P65" s="75"/>
+      <c r="Q65" s="75"/>
+      <c r="R65" s="75"/>
+      <c r="S65" s="75"/>
       <c r="T65" s="51"/>
       <c r="U65" s="25"/>
       <c r="V65" s="25"/>
@@ -5633,17 +5633,17 @@
       <c r="H66" s="25"/>
       <c r="I66" s="25"/>
       <c r="J66" s="25"/>
-      <c r="K66" s="65" t="s">
+      <c r="K66" s="74" t="s">
         <v>267</v>
       </c>
-      <c r="L66" s="66"/>
-      <c r="M66" s="66"/>
-      <c r="N66" s="66"/>
-      <c r="O66" s="66"/>
-      <c r="P66" s="66"/>
-      <c r="Q66" s="66"/>
-      <c r="R66" s="66"/>
-      <c r="S66" s="66"/>
+      <c r="L66" s="75"/>
+      <c r="M66" s="75"/>
+      <c r="N66" s="75"/>
+      <c r="O66" s="75"/>
+      <c r="P66" s="75"/>
+      <c r="Q66" s="75"/>
+      <c r="R66" s="75"/>
+      <c r="S66" s="75"/>
       <c r="T66" s="51"/>
       <c r="U66" s="25"/>
       <c r="V66" s="25"/>
@@ -5670,17 +5670,17 @@
       <c r="H67" s="25"/>
       <c r="I67" s="25"/>
       <c r="J67" s="25"/>
-      <c r="K67" s="65" t="s">
+      <c r="K67" s="74" t="s">
         <v>268</v>
       </c>
-      <c r="L67" s="66"/>
-      <c r="M67" s="66"/>
-      <c r="N67" s="66"/>
-      <c r="O67" s="66"/>
-      <c r="P67" s="66"/>
-      <c r="Q67" s="66"/>
-      <c r="R67" s="66"/>
-      <c r="S67" s="66"/>
+      <c r="L67" s="75"/>
+      <c r="M67" s="75"/>
+      <c r="N67" s="75"/>
+      <c r="O67" s="75"/>
+      <c r="P67" s="75"/>
+      <c r="Q67" s="75"/>
+      <c r="R67" s="75"/>
+      <c r="S67" s="75"/>
       <c r="T67" s="51"/>
       <c r="U67" s="25"/>
       <c r="V67" s="25"/>
@@ -5707,17 +5707,17 @@
       <c r="H68" s="25"/>
       <c r="I68" s="25"/>
       <c r="J68" s="25"/>
-      <c r="K68" s="65" t="s">
+      <c r="K68" s="74" t="s">
         <v>269</v>
       </c>
-      <c r="L68" s="66"/>
-      <c r="M68" s="66"/>
-      <c r="N68" s="66"/>
-      <c r="O68" s="66"/>
-      <c r="P68" s="66"/>
-      <c r="Q68" s="66"/>
-      <c r="R68" s="66"/>
-      <c r="S68" s="66"/>
+      <c r="L68" s="75"/>
+      <c r="M68" s="75"/>
+      <c r="N68" s="75"/>
+      <c r="O68" s="75"/>
+      <c r="P68" s="75"/>
+      <c r="Q68" s="75"/>
+      <c r="R68" s="75"/>
+      <c r="S68" s="75"/>
       <c r="T68" s="51"/>
       <c r="U68" s="25"/>
       <c r="V68" s="25"/>
@@ -5744,17 +5744,17 @@
       <c r="H69" s="25"/>
       <c r="I69" s="25"/>
       <c r="J69" s="25"/>
-      <c r="K69" s="65" t="s">
+      <c r="K69" s="74" t="s">
         <v>270</v>
       </c>
-      <c r="L69" s="66"/>
-      <c r="M69" s="66"/>
-      <c r="N69" s="66"/>
-      <c r="O69" s="66"/>
-      <c r="P69" s="66"/>
-      <c r="Q69" s="66"/>
-      <c r="R69" s="66"/>
-      <c r="S69" s="66"/>
+      <c r="L69" s="75"/>
+      <c r="M69" s="75"/>
+      <c r="N69" s="75"/>
+      <c r="O69" s="75"/>
+      <c r="P69" s="75"/>
+      <c r="Q69" s="75"/>
+      <c r="R69" s="75"/>
+      <c r="S69" s="75"/>
       <c r="T69" s="51"/>
       <c r="U69" s="25"/>
       <c r="V69" s="25"/>
@@ -5781,17 +5781,17 @@
       <c r="H70" s="25"/>
       <c r="I70" s="25"/>
       <c r="J70" s="25"/>
-      <c r="K70" s="65" t="s">
+      <c r="K70" s="74" t="s">
         <v>271</v>
       </c>
-      <c r="L70" s="66"/>
-      <c r="M70" s="66"/>
-      <c r="N70" s="66"/>
-      <c r="O70" s="66"/>
-      <c r="P70" s="66"/>
-      <c r="Q70" s="66"/>
-      <c r="R70" s="66"/>
-      <c r="S70" s="66"/>
+      <c r="L70" s="75"/>
+      <c r="M70" s="75"/>
+      <c r="N70" s="75"/>
+      <c r="O70" s="75"/>
+      <c r="P70" s="75"/>
+      <c r="Q70" s="75"/>
+      <c r="R70" s="75"/>
+      <c r="S70" s="75"/>
       <c r="T70" s="51"/>
       <c r="U70" s="25"/>
       <c r="V70" s="25"/>
@@ -5818,17 +5818,17 @@
       <c r="H71" s="25"/>
       <c r="I71" s="25"/>
       <c r="J71" s="25"/>
-      <c r="K71" s="65" t="s">
+      <c r="K71" s="74" t="s">
         <v>272</v>
       </c>
-      <c r="L71" s="66"/>
-      <c r="M71" s="66"/>
-      <c r="N71" s="66"/>
-      <c r="O71" s="66"/>
-      <c r="P71" s="66"/>
-      <c r="Q71" s="66"/>
-      <c r="R71" s="66"/>
-      <c r="S71" s="66"/>
+      <c r="L71" s="75"/>
+      <c r="M71" s="75"/>
+      <c r="N71" s="75"/>
+      <c r="O71" s="75"/>
+      <c r="P71" s="75"/>
+      <c r="Q71" s="75"/>
+      <c r="R71" s="75"/>
+      <c r="S71" s="75"/>
       <c r="T71" s="51"/>
       <c r="U71" s="25"/>
       <c r="V71" s="25"/>
@@ -5855,17 +5855,17 @@
       <c r="H72" s="25"/>
       <c r="I72" s="25"/>
       <c r="J72" s="25"/>
-      <c r="K72" s="65" t="s">
+      <c r="K72" s="74" t="s">
         <v>273</v>
       </c>
-      <c r="L72" s="66"/>
-      <c r="M72" s="66"/>
-      <c r="N72" s="66"/>
-      <c r="O72" s="66"/>
-      <c r="P72" s="66"/>
-      <c r="Q72" s="66"/>
-      <c r="R72" s="66"/>
-      <c r="S72" s="66"/>
+      <c r="L72" s="75"/>
+      <c r="M72" s="75"/>
+      <c r="N72" s="75"/>
+      <c r="O72" s="75"/>
+      <c r="P72" s="75"/>
+      <c r="Q72" s="75"/>
+      <c r="R72" s="75"/>
+      <c r="S72" s="75"/>
       <c r="T72" s="51"/>
       <c r="U72" s="25"/>
       <c r="V72" s="25"/>
@@ -5892,17 +5892,17 @@
       <c r="H73" s="25"/>
       <c r="I73" s="25"/>
       <c r="J73" s="25"/>
-      <c r="K73" s="65" t="s">
+      <c r="K73" s="74" t="s">
         <v>274</v>
       </c>
-      <c r="L73" s="66"/>
-      <c r="M73" s="66"/>
-      <c r="N73" s="66"/>
-      <c r="O73" s="66"/>
-      <c r="P73" s="66"/>
-      <c r="Q73" s="66"/>
-      <c r="R73" s="66"/>
-      <c r="S73" s="66"/>
+      <c r="L73" s="75"/>
+      <c r="M73" s="75"/>
+      <c r="N73" s="75"/>
+      <c r="O73" s="75"/>
+      <c r="P73" s="75"/>
+      <c r="Q73" s="75"/>
+      <c r="R73" s="75"/>
+      <c r="S73" s="75"/>
       <c r="T73" s="51"/>
       <c r="U73" s="25"/>
       <c r="V73" s="25"/>
@@ -5929,17 +5929,17 @@
       <c r="H74" s="25"/>
       <c r="I74" s="25"/>
       <c r="J74" s="25"/>
-      <c r="K74" s="65" t="s">
+      <c r="K74" s="74" t="s">
         <v>275</v>
       </c>
-      <c r="L74" s="66"/>
-      <c r="M74" s="66"/>
-      <c r="N74" s="66"/>
-      <c r="O74" s="66"/>
-      <c r="P74" s="66"/>
-      <c r="Q74" s="66"/>
-      <c r="R74" s="66"/>
-      <c r="S74" s="66"/>
+      <c r="L74" s="75"/>
+      <c r="M74" s="75"/>
+      <c r="N74" s="75"/>
+      <c r="O74" s="75"/>
+      <c r="P74" s="75"/>
+      <c r="Q74" s="75"/>
+      <c r="R74" s="75"/>
+      <c r="S74" s="75"/>
       <c r="T74" s="51"/>
       <c r="U74" s="25"/>
       <c r="V74" s="25"/>
@@ -5966,17 +5966,17 @@
       <c r="H75" s="25"/>
       <c r="I75" s="25"/>
       <c r="J75" s="25"/>
-      <c r="K75" s="65" t="s">
+      <c r="K75" s="74" t="s">
         <v>276</v>
       </c>
-      <c r="L75" s="66"/>
-      <c r="M75" s="66"/>
-      <c r="N75" s="66"/>
-      <c r="O75" s="66"/>
-      <c r="P75" s="66"/>
-      <c r="Q75" s="66"/>
-      <c r="R75" s="66"/>
-      <c r="S75" s="66"/>
+      <c r="L75" s="75"/>
+      <c r="M75" s="75"/>
+      <c r="N75" s="75"/>
+      <c r="O75" s="75"/>
+      <c r="P75" s="75"/>
+      <c r="Q75" s="75"/>
+      <c r="R75" s="75"/>
+      <c r="S75" s="75"/>
       <c r="T75" s="51"/>
       <c r="U75" s="25"/>
       <c r="V75" s="25"/>
@@ -6003,17 +6003,17 @@
       <c r="H76" s="25"/>
       <c r="I76" s="25"/>
       <c r="J76" s="25"/>
-      <c r="K76" s="65" t="s">
+      <c r="K76" s="74" t="s">
         <v>277</v>
       </c>
-      <c r="L76" s="66"/>
-      <c r="M76" s="66"/>
-      <c r="N76" s="66"/>
-      <c r="O76" s="66"/>
-      <c r="P76" s="66"/>
-      <c r="Q76" s="66"/>
-      <c r="R76" s="66"/>
-      <c r="S76" s="66"/>
+      <c r="L76" s="75"/>
+      <c r="M76" s="75"/>
+      <c r="N76" s="75"/>
+      <c r="O76" s="75"/>
+      <c r="P76" s="75"/>
+      <c r="Q76" s="75"/>
+      <c r="R76" s="75"/>
+      <c r="S76" s="75"/>
       <c r="T76" s="51"/>
       <c r="U76" s="25"/>
       <c r="V76" s="25"/>
@@ -6042,15 +6042,15 @@
       <c r="J77" s="25"/>
       <c r="K77" s="25"/>
       <c r="L77" s="25"/>
-      <c r="M77" s="65" t="s">
+      <c r="M77" s="74" t="s">
         <v>278</v>
       </c>
-      <c r="N77" s="66"/>
-      <c r="O77" s="66"/>
-      <c r="P77" s="66"/>
-      <c r="Q77" s="66"/>
-      <c r="R77" s="66"/>
-      <c r="S77" s="66"/>
+      <c r="N77" s="75"/>
+      <c r="O77" s="75"/>
+      <c r="P77" s="75"/>
+      <c r="Q77" s="75"/>
+      <c r="R77" s="75"/>
+      <c r="S77" s="75"/>
       <c r="T77" s="51"/>
       <c r="U77" s="25"/>
       <c r="V77" s="25"/>
@@ -6079,15 +6079,15 @@
       <c r="J78" s="25"/>
       <c r="K78" s="25"/>
       <c r="L78" s="25"/>
-      <c r="M78" s="65" t="s">
+      <c r="M78" s="74" t="s">
         <v>279</v>
       </c>
-      <c r="N78" s="66"/>
-      <c r="O78" s="66"/>
-      <c r="P78" s="66"/>
-      <c r="Q78" s="66"/>
-      <c r="R78" s="66"/>
-      <c r="S78" s="66"/>
+      <c r="N78" s="75"/>
+      <c r="O78" s="75"/>
+      <c r="P78" s="75"/>
+      <c r="Q78" s="75"/>
+      <c r="R78" s="75"/>
+      <c r="S78" s="75"/>
       <c r="T78" s="51"/>
       <c r="U78" s="25"/>
       <c r="V78" s="25"/>
@@ -6116,15 +6116,15 @@
       <c r="J79" s="25"/>
       <c r="K79" s="25"/>
       <c r="L79" s="25"/>
-      <c r="M79" s="65" t="s">
+      <c r="M79" s="74" t="s">
         <v>280</v>
       </c>
-      <c r="N79" s="66"/>
-      <c r="O79" s="66"/>
-      <c r="P79" s="66"/>
-      <c r="Q79" s="66"/>
-      <c r="R79" s="66"/>
-      <c r="S79" s="66"/>
+      <c r="N79" s="75"/>
+      <c r="O79" s="75"/>
+      <c r="P79" s="75"/>
+      <c r="Q79" s="75"/>
+      <c r="R79" s="75"/>
+      <c r="S79" s="75"/>
       <c r="T79" s="51"/>
       <c r="U79" s="25"/>
       <c r="V79" s="25"/>
@@ -6153,15 +6153,15 @@
       <c r="J80" s="25"/>
       <c r="K80" s="25"/>
       <c r="L80" s="25"/>
-      <c r="M80" s="65" t="s">
+      <c r="M80" s="74" t="s">
         <v>281</v>
       </c>
-      <c r="N80" s="66"/>
-      <c r="O80" s="66"/>
-      <c r="P80" s="66"/>
-      <c r="Q80" s="66"/>
-      <c r="R80" s="66"/>
-      <c r="S80" s="66"/>
+      <c r="N80" s="75"/>
+      <c r="O80" s="75"/>
+      <c r="P80" s="75"/>
+      <c r="Q80" s="75"/>
+      <c r="R80" s="75"/>
+      <c r="S80" s="75"/>
       <c r="T80" s="51"/>
       <c r="U80" s="25"/>
       <c r="V80" s="25"/>
@@ -6193,15 +6193,15 @@
       <c r="J81" s="25"/>
       <c r="K81" s="25"/>
       <c r="L81" s="25"/>
-      <c r="M81" s="65" t="s">
+      <c r="M81" s="74" t="s">
         <v>282</v>
       </c>
-      <c r="N81" s="66"/>
-      <c r="O81" s="66"/>
-      <c r="P81" s="66"/>
-      <c r="Q81" s="66"/>
-      <c r="R81" s="66"/>
-      <c r="S81" s="66"/>
+      <c r="N81" s="75"/>
+      <c r="O81" s="75"/>
+      <c r="P81" s="75"/>
+      <c r="Q81" s="75"/>
+      <c r="R81" s="75"/>
+      <c r="S81" s="75"/>
       <c r="T81" s="51"/>
       <c r="U81" s="25"/>
       <c r="V81" s="25"/>
@@ -6230,15 +6230,15 @@
       <c r="J82" s="25"/>
       <c r="K82" s="25"/>
       <c r="L82" s="25"/>
-      <c r="M82" s="65" t="s">
+      <c r="M82" s="74" t="s">
         <v>283</v>
       </c>
-      <c r="N82" s="66"/>
-      <c r="O82" s="66"/>
-      <c r="P82" s="66"/>
-      <c r="Q82" s="66"/>
-      <c r="R82" s="66"/>
-      <c r="S82" s="66"/>
+      <c r="N82" s="75"/>
+      <c r="O82" s="75"/>
+      <c r="P82" s="75"/>
+      <c r="Q82" s="75"/>
+      <c r="R82" s="75"/>
+      <c r="S82" s="75"/>
       <c r="T82" s="51"/>
       <c r="U82" s="25"/>
       <c r="V82" s="25"/>
@@ -6267,15 +6267,15 @@
       <c r="J83" s="25"/>
       <c r="K83" s="25"/>
       <c r="L83" s="25"/>
-      <c r="M83" s="65" t="s">
+      <c r="M83" s="74" t="s">
         <v>284</v>
       </c>
-      <c r="N83" s="66"/>
-      <c r="O83" s="66"/>
-      <c r="P83" s="66"/>
-      <c r="Q83" s="66"/>
-      <c r="R83" s="66"/>
-      <c r="S83" s="66"/>
+      <c r="N83" s="75"/>
+      <c r="O83" s="75"/>
+      <c r="P83" s="75"/>
+      <c r="Q83" s="75"/>
+      <c r="R83" s="75"/>
+      <c r="S83" s="75"/>
       <c r="T83" s="51"/>
       <c r="U83" s="25"/>
       <c r="V83" s="25"/>
@@ -6304,15 +6304,15 @@
       <c r="J84" s="25"/>
       <c r="K84" s="25"/>
       <c r="L84" s="25"/>
-      <c r="M84" s="65" t="s">
+      <c r="M84" s="74" t="s">
         <v>285</v>
       </c>
-      <c r="N84" s="66"/>
-      <c r="O84" s="66"/>
-      <c r="P84" s="66"/>
-      <c r="Q84" s="66"/>
-      <c r="R84" s="66"/>
-      <c r="S84" s="66"/>
+      <c r="N84" s="75"/>
+      <c r="O84" s="75"/>
+      <c r="P84" s="75"/>
+      <c r="Q84" s="75"/>
+      <c r="R84" s="75"/>
+      <c r="S84" s="75"/>
       <c r="T84" s="51"/>
       <c r="U84" s="25"/>
       <c r="V84" s="25"/>
@@ -6339,15 +6339,15 @@
       <c r="J85" s="25"/>
       <c r="K85" s="25"/>
       <c r="L85" s="25"/>
-      <c r="M85" s="65" t="s">
+      <c r="M85" s="74" t="s">
         <v>286</v>
       </c>
-      <c r="N85" s="66"/>
-      <c r="O85" s="66"/>
-      <c r="P85" s="66"/>
-      <c r="Q85" s="66"/>
-      <c r="R85" s="66"/>
-      <c r="S85" s="66"/>
+      <c r="N85" s="75"/>
+      <c r="O85" s="75"/>
+      <c r="P85" s="75"/>
+      <c r="Q85" s="75"/>
+      <c r="R85" s="75"/>
+      <c r="S85" s="75"/>
       <c r="T85" s="51"/>
       <c r="U85" s="25"/>
       <c r="V85" s="25"/>
@@ -6374,15 +6374,15 @@
       <c r="J86" s="25"/>
       <c r="K86" s="25"/>
       <c r="L86" s="25"/>
-      <c r="M86" s="65" t="s">
+      <c r="M86" s="74" t="s">
         <v>287</v>
       </c>
-      <c r="N86" s="66"/>
-      <c r="O86" s="66"/>
-      <c r="P86" s="66"/>
-      <c r="Q86" s="66"/>
-      <c r="R86" s="66"/>
-      <c r="S86" s="66"/>
+      <c r="N86" s="75"/>
+      <c r="O86" s="75"/>
+      <c r="P86" s="75"/>
+      <c r="Q86" s="75"/>
+      <c r="R86" s="75"/>
+      <c r="S86" s="75"/>
       <c r="T86" s="51"/>
       <c r="U86" s="25"/>
       <c r="V86" s="25"/>
@@ -6409,15 +6409,15 @@
       <c r="J87" s="25"/>
       <c r="K87" s="25"/>
       <c r="L87" s="25"/>
-      <c r="M87" s="65" t="s">
+      <c r="M87" s="74" t="s">
         <v>288</v>
       </c>
-      <c r="N87" s="66"/>
-      <c r="O87" s="66"/>
-      <c r="P87" s="66"/>
-      <c r="Q87" s="66"/>
-      <c r="R87" s="66"/>
-      <c r="S87" s="66"/>
+      <c r="N87" s="75"/>
+      <c r="O87" s="75"/>
+      <c r="P87" s="75"/>
+      <c r="Q87" s="75"/>
+      <c r="R87" s="75"/>
+      <c r="S87" s="75"/>
       <c r="T87" s="51"/>
       <c r="U87" s="25"/>
       <c r="V87" s="25"/>
@@ -6445,15 +6445,15 @@
       <c r="J88" s="25"/>
       <c r="K88" s="25"/>
       <c r="L88" s="25"/>
-      <c r="M88" s="65" t="s">
+      <c r="M88" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="N88" s="66"/>
-      <c r="O88" s="66"/>
-      <c r="P88" s="66"/>
-      <c r="Q88" s="66"/>
-      <c r="R88" s="66"/>
-      <c r="S88" s="66"/>
+      <c r="N88" s="75"/>
+      <c r="O88" s="75"/>
+      <c r="P88" s="75"/>
+      <c r="Q88" s="75"/>
+      <c r="R88" s="75"/>
+      <c r="S88" s="75"/>
       <c r="T88" s="51"/>
       <c r="U88" s="25"/>
       <c r="V88" s="25"/>
@@ -6476,20 +6476,20 @@
       <c r="F89" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H89" s="67" t="s">
+      <c r="H89" s="97" t="s">
         <v>307</v>
       </c>
-      <c r="I89" s="67"/>
-      <c r="J89" s="67"/>
-      <c r="K89" s="67"/>
-      <c r="L89" s="67"/>
-      <c r="M89" s="67"/>
-      <c r="N89" s="67"/>
-      <c r="O89" s="67"/>
-      <c r="P89" s="67"/>
-      <c r="Q89" s="67"/>
-      <c r="R89" s="67"/>
-      <c r="S89" s="65"/>
+      <c r="I89" s="97"/>
+      <c r="J89" s="97"/>
+      <c r="K89" s="97"/>
+      <c r="L89" s="97"/>
+      <c r="M89" s="97"/>
+      <c r="N89" s="97"/>
+      <c r="O89" s="97"/>
+      <c r="P89" s="97"/>
+      <c r="Q89" s="97"/>
+      <c r="R89" s="97"/>
+      <c r="S89" s="74"/>
       <c r="T89" s="51"/>
       <c r="U89" s="25"/>
       <c r="V89" s="25"/>
@@ -6514,20 +6514,20 @@
         <v>19</v>
       </c>
       <c r="G90" s="10"/>
-      <c r="H90" s="63" t="s">
+      <c r="H90" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="I90" s="63"/>
-      <c r="J90" s="63"/>
-      <c r="K90" s="63"/>
-      <c r="L90" s="63"/>
-      <c r="M90" s="63"/>
-      <c r="N90" s="63"/>
-      <c r="O90" s="63"/>
-      <c r="P90" s="63"/>
-      <c r="Q90" s="63"/>
-      <c r="R90" s="63"/>
-      <c r="S90" s="64"/>
+      <c r="I90" s="102"/>
+      <c r="J90" s="102"/>
+      <c r="K90" s="102"/>
+      <c r="L90" s="102"/>
+      <c r="M90" s="102"/>
+      <c r="N90" s="102"/>
+      <c r="O90" s="102"/>
+      <c r="P90" s="102"/>
+      <c r="Q90" s="102"/>
+      <c r="R90" s="102"/>
+      <c r="S90" s="103"/>
       <c r="T90" s="51"/>
       <c r="U90" s="25"/>
       <c r="V90" s="25"/>
@@ -6550,6 +6550,101 @@
     </row>
   </sheetData>
   <mergeCells count="119">
+    <mergeCell ref="H90:S90"/>
+    <mergeCell ref="M85:S85"/>
+    <mergeCell ref="M86:S86"/>
+    <mergeCell ref="M87:S87"/>
+    <mergeCell ref="M88:S88"/>
+    <mergeCell ref="H89:S89"/>
+    <mergeCell ref="L64:O64"/>
+    <mergeCell ref="P64:S64"/>
+    <mergeCell ref="K73:S73"/>
+    <mergeCell ref="K74:S74"/>
+    <mergeCell ref="K75:S75"/>
+    <mergeCell ref="K69:S69"/>
+    <mergeCell ref="K70:S70"/>
+    <mergeCell ref="K71:S71"/>
+    <mergeCell ref="K72:S72"/>
+    <mergeCell ref="M77:S77"/>
+    <mergeCell ref="M78:S78"/>
+    <mergeCell ref="M79:S79"/>
+    <mergeCell ref="K76:S76"/>
+    <mergeCell ref="M80:S80"/>
+    <mergeCell ref="M81:S81"/>
+    <mergeCell ref="M82:S82"/>
+    <mergeCell ref="M83:S83"/>
+    <mergeCell ref="M84:S84"/>
+    <mergeCell ref="H56:S56"/>
+    <mergeCell ref="L61:S61"/>
+    <mergeCell ref="J62:N62"/>
+    <mergeCell ref="O62:S62"/>
+    <mergeCell ref="H63:L63"/>
+    <mergeCell ref="O63:S63"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="L51:N51"/>
+    <mergeCell ref="P52:S52"/>
+    <mergeCell ref="H53:S53"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="P54:S54"/>
+    <mergeCell ref="H44:S44"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="P45:S45"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="J34:S34"/>
+    <mergeCell ref="J35:S35"/>
+    <mergeCell ref="I36:S36"/>
+    <mergeCell ref="H37:S37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="L38:S38"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="K32:S32"/>
+    <mergeCell ref="J33:S33"/>
+    <mergeCell ref="H40:S40"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="H13:S13"/>
+    <mergeCell ref="J24:N24"/>
+    <mergeCell ref="O24:S24"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="J22:N22"/>
+    <mergeCell ref="O22:S22"/>
+    <mergeCell ref="J23:N23"/>
+    <mergeCell ref="O23:S23"/>
+    <mergeCell ref="H14:S14"/>
+    <mergeCell ref="H15:S15"/>
+    <mergeCell ref="H16:S16"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:O28"/>
+    <mergeCell ref="P28:S28"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="P29:S29"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="O20:S20"/>
+    <mergeCell ref="H17:S17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="Q25:S25"/>
     <mergeCell ref="O3:S3"/>
     <mergeCell ref="O5:S5"/>
     <mergeCell ref="H6:K6"/>
@@ -6574,101 +6669,6 @@
     <mergeCell ref="J19:N19"/>
     <mergeCell ref="O19:S19"/>
     <mergeCell ref="J20:N20"/>
-    <mergeCell ref="O20:S20"/>
-    <mergeCell ref="H17:S17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="H40:S40"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="H13:S13"/>
-    <mergeCell ref="J24:N24"/>
-    <mergeCell ref="O24:S24"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="J22:N22"/>
-    <mergeCell ref="O22:S22"/>
-    <mergeCell ref="J23:N23"/>
-    <mergeCell ref="O23:S23"/>
-    <mergeCell ref="H14:S14"/>
-    <mergeCell ref="H15:S15"/>
-    <mergeCell ref="H16:S16"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:O28"/>
-    <mergeCell ref="P28:S28"/>
-    <mergeCell ref="L29:O29"/>
-    <mergeCell ref="P29:S29"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="J34:S34"/>
-    <mergeCell ref="J35:S35"/>
-    <mergeCell ref="I36:S36"/>
-    <mergeCell ref="H37:S37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="L38:S38"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="K32:S32"/>
-    <mergeCell ref="J33:S33"/>
-    <mergeCell ref="H44:S44"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="P45:S45"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="H56:S56"/>
-    <mergeCell ref="L61:S61"/>
-    <mergeCell ref="J62:N62"/>
-    <mergeCell ref="O62:S62"/>
-    <mergeCell ref="H63:L63"/>
-    <mergeCell ref="O63:S63"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="L51:N51"/>
-    <mergeCell ref="P52:S52"/>
-    <mergeCell ref="H53:S53"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="P54:S54"/>
-    <mergeCell ref="H90:S90"/>
-    <mergeCell ref="M85:S85"/>
-    <mergeCell ref="M86:S86"/>
-    <mergeCell ref="M87:S87"/>
-    <mergeCell ref="M88:S88"/>
-    <mergeCell ref="H89:S89"/>
-    <mergeCell ref="L64:O64"/>
-    <mergeCell ref="P64:S64"/>
-    <mergeCell ref="K73:S73"/>
-    <mergeCell ref="K74:S74"/>
-    <mergeCell ref="K75:S75"/>
-    <mergeCell ref="K69:S69"/>
-    <mergeCell ref="K70:S70"/>
-    <mergeCell ref="K71:S71"/>
-    <mergeCell ref="K72:S72"/>
-    <mergeCell ref="M77:S77"/>
-    <mergeCell ref="M78:S78"/>
-    <mergeCell ref="M79:S79"/>
-    <mergeCell ref="K76:S76"/>
-    <mergeCell ref="M80:S80"/>
-    <mergeCell ref="M81:S81"/>
-    <mergeCell ref="M82:S82"/>
-    <mergeCell ref="M83:S83"/>
-    <mergeCell ref="M84:S84"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
